--- a/docs/StructureDefinition-internal-jugular-vein-flow-observation.xlsx
+++ b/docs/StructureDefinition-internal-jugular-vein-flow-observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-internal-jugular-vein-flow-observation.xlsx
+++ b/docs/StructureDefinition-internal-jugular-vein-flow-observation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2761" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2762" uniqueCount="539">
   <si>
     <t>Property</t>
   </si>
@@ -27,13 +27,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/StructureDefinition/internal-jugular-vein-flow-observation</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/internal-jugular-vein-flow-observation</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -471,7 +474,7 @@
     <t>gravityContext</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://mitre.org/fhir/space-health/StructureDefinition/gravity-context}
+    <t xml:space="preserve">Extension {https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/gravity-context}
 </t>
   </si>
   <si>
@@ -491,7 +494,7 @@
     <t>missionContext</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/aerospace/StructureDefinition/mission-context}
+    <t xml:space="preserve">Extension {https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/mission-context}
 </t>
   </si>
   <si>
@@ -507,7 +510,7 @@
     <t>flightDay</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://mitre.org/fhir/space-health/StructureDefinition/flight-day}
+    <t xml:space="preserve">Extension {https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/flight-day}
 </t>
   </si>
   <si>
@@ -523,7 +526,7 @@
     <t>lbnpPressureLevel</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://mitre.org/fhir/space-health/StructureDefinition/lbnp-pressure-level}
+    <t xml:space="preserve">Extension {https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/lbnp-pressure-level}
 </t>
   </si>
   <si>
@@ -761,7 +764,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://mitre.org/fhir/space-health/StructureDefinition/Astronaut)
+    <t xml:space="preserve">Reference(https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/astronaut)
 </t>
   </si>
   <si>
@@ -949,7 +952,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/ValueSet/ijv-flow-grade-vs</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/ValueSet/ijv-flow-grade-vs</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7
@@ -1525,9 +1528,9 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://loinc.org"/&gt;
-    &lt;code value="LP74840-2"/&gt;
-    &lt;display value="Flow velocity"/&gt;
+    &lt;system value="https://awatson1978.github.io/aerospace-medicine-ig/CodeSystem/venous-flow-metric-cs"/&gt;
+    &lt;code value="fdi-ratio"/&gt;
+    &lt;display value="Flow Directionality Index"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
@@ -1963,54 +1966,56 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2048,7 +2053,7 @@
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="53.24609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.50390625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="65.4921875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
@@ -2068,149 +2073,149 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AO1" t="s" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AP1" t="s" s="1">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -2222,16 +2227,16 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -2281,31 +2286,31 @@
         <v>20</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AO2" t="s" s="2">
         <v>20</v>
@@ -2316,10 +2321,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2327,10 +2332,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -2339,19 +2344,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2401,13 +2406,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -2436,10 +2441,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2447,10 +2452,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -2459,16 +2464,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2519,19 +2524,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -2554,10 +2559,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2565,31 +2570,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2639,19 +2644,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -2674,10 +2679,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2685,10 +2690,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -2700,16 +2705,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2735,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -2759,19 +2764,19 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -2794,21 +2799,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -2820,16 +2825,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2879,19 +2884,19 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -2903,7 +2908,7 @@
         <v>20</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>20</v>
@@ -2914,21 +2919,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -2940,16 +2945,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2999,13 +3004,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -3023,7 +3028,7 @@
         <v>20</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>20</v>
@@ -3034,10 +3039,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -3045,10 +3050,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -3060,13 +3065,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -3105,29 +3110,29 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -3150,26 +3155,26 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>20</v>
@@ -3178,13 +3183,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -3235,19 +3240,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -3270,26 +3275,26 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>20</v>
@@ -3298,13 +3303,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3355,19 +3360,19 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>20</v>
@@ -3390,26 +3395,26 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>20</v>
@@ -3418,13 +3423,13 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3475,19 +3480,19 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>20</v>
@@ -3510,26 +3515,26 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>20</v>
@@ -3538,13 +3543,13 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3595,19 +3600,19 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>20</v>
@@ -3630,45 +3635,45 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -3717,19 +3722,19 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>20</v>
@@ -3741,7 +3746,7 @@
         <v>20</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>20</v>
@@ -3752,10 +3757,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3763,10 +3768,10 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -3775,20 +3780,20 @@
         <v>20</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>20</v>
@@ -3837,34 +3842,34 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>20</v>
@@ -3872,21 +3877,21 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
@@ -3895,20 +3900,20 @@
         <v>20</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3957,31 +3962,31 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>20</v>
@@ -3992,21 +3997,21 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -4015,19 +4020,19 @@
         <v>20</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4077,31 +4082,31 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>20</v>
@@ -4112,10 +4117,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4123,34 +4128,34 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -4175,13 +4180,13 @@
         <v>20</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>20</v>
@@ -4199,34 +4204,34 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>20</v>
@@ -4234,10 +4239,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4245,13 +4250,13 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>20</v>
@@ -4260,19 +4265,19 @@
         <v>20</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -4297,13 +4302,13 @@
         <v>20</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>20</v>
@@ -4321,19 +4326,19 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>20</v>
@@ -4345,10 +4350,10 @@
         <v>20</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>20</v>
@@ -4356,45 +4361,45 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -4419,13 +4424,13 @@
         <v>20</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>20</v>
@@ -4443,45 +4448,45 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4489,34 +4494,34 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -4565,34 +4570,34 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>20</v>
@@ -4600,10 +4605,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4611,10 +4616,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -4623,19 +4628,19 @@
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4685,34 +4690,34 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="AG22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ22" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>20</v>
@@ -4720,21 +4725,21 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -4743,22 +4748,22 @@
         <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -4807,34 +4812,34 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>20</v>
@@ -4842,45 +4847,45 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -4929,34 +4934,34 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>20</v>
@@ -4964,10 +4969,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4975,10 +4980,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -4987,19 +4992,19 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5049,19 +5054,19 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>20</v>
@@ -5070,13 +5075,13 @@
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>20</v>
@@ -5084,10 +5089,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5095,10 +5100,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -5107,20 +5112,20 @@
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -5169,34 +5174,34 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>20</v>
@@ -5204,10 +5209,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5215,34 +5220,34 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -5267,11 +5272,11 @@
         <v>20</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>20</v>
@@ -5289,45 +5294,45 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5335,10 +5340,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -5350,19 +5355,19 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -5387,13 +5392,13 @@
         <v>20</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>20</v>
@@ -5411,19 +5416,19 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>20</v>
@@ -5432,10 +5437,10 @@
         <v>20</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>20</v>
@@ -5446,21 +5451,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -5472,19 +5477,19 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5509,13 +5514,13 @@
         <v>20</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>20</v>
@@ -5533,45 +5538,45 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5579,10 +5584,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -5594,19 +5599,19 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5655,19 +5660,19 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>20</v>
@@ -5676,10 +5681,10 @@
         <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>20</v>
@@ -5690,10 +5695,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5701,13 +5706,13 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>20</v>
@@ -5716,16 +5721,16 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5751,13 +5756,13 @@
         <v>20</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>20</v>
@@ -5775,45 +5780,45 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5821,10 +5826,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
@@ -5836,19 +5841,19 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5873,13 +5878,13 @@
         <v>20</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>20</v>
@@ -5897,19 +5902,19 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
@@ -5918,10 +5923,10 @@
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
@@ -5932,10 +5937,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5943,10 +5948,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5958,16 +5963,16 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6017,45 +6022,45 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6063,10 +6068,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -6078,16 +6083,16 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6137,45 +6142,45 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6183,10 +6188,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -6198,19 +6203,19 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -6259,19 +6264,19 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>20</v>
@@ -6280,10 +6285,10 @@
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
@@ -6294,10 +6299,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6305,10 +6310,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -6320,13 +6325,13 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6377,13 +6382,13 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
@@ -6401,7 +6406,7 @@
         <v>20</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
@@ -6412,21 +6417,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -6438,16 +6443,16 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6497,19 +6502,19 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>20</v>
@@ -6521,7 +6526,7 @@
         <v>20</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
@@ -6532,45 +6537,45 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6619,19 +6624,19 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
@@ -6643,7 +6648,7 @@
         <v>20</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
@@ -6654,10 +6659,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6665,10 +6670,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6680,13 +6685,13 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6737,19 +6742,19 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
@@ -6758,10 +6763,10 @@
         <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
@@ -6772,10 +6777,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6783,10 +6788,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6798,13 +6803,13 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6855,19 +6860,19 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>20</v>
@@ -6876,10 +6881,10 @@
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>20</v>
@@ -6890,10 +6895,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6901,10 +6906,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6916,19 +6921,19 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6953,13 +6958,13 @@
         <v>20</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>20</v>
@@ -6977,31 +6982,31 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>20</v>
@@ -7012,10 +7017,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7023,10 +7028,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>20</v>
@@ -7038,19 +7043,19 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -7075,13 +7080,13 @@
         <v>20</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>20</v>
@@ -7099,31 +7104,31 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="AG42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>413</v>
-      </c>
       <c r="AN42" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>20</v>
@@ -7134,10 +7139,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7145,10 +7150,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -7160,17 +7165,17 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -7219,19 +7224,19 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>20</v>
@@ -7243,7 +7248,7 @@
         <v>20</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>20</v>
@@ -7254,10 +7259,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7265,10 +7270,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
@@ -7280,13 +7285,13 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7337,19 +7342,19 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>20</v>
@@ -7358,10 +7363,10 @@
         <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>20</v>
@@ -7372,10 +7377,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7383,10 +7388,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -7395,19 +7400,19 @@
         <v>20</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7457,19 +7462,19 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>20</v>
@@ -7478,10 +7483,10 @@
         <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
@@ -7492,10 +7497,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7503,10 +7508,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -7515,19 +7520,19 @@
         <v>20</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7577,19 +7582,19 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>20</v>
@@ -7598,10 +7603,10 @@
         <v>20</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>20</v>
@@ -7612,10 +7617,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7623,10 +7628,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
@@ -7635,22 +7640,22 @@
         <v>20</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7687,29 +7692,29 @@
         <v>20</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AC47" s="2"/>
       <c r="AD47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>20</v>
@@ -7718,10 +7723,10 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>20</v>
@@ -7732,10 +7737,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7743,10 +7748,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
@@ -7758,13 +7763,13 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7815,13 +7820,13 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>20</v>
@@ -7839,7 +7844,7 @@
         <v>20</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>20</v>
@@ -7850,21 +7855,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -7876,16 +7881,16 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7935,19 +7940,19 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>20</v>
@@ -7959,7 +7964,7 @@
         <v>20</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>20</v>
@@ -7970,45 +7975,45 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -8057,19 +8062,19 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>20</v>
@@ -8081,7 +8086,7 @@
         <v>20</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>20</v>
@@ -8092,10 +8097,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8103,10 +8108,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -8115,22 +8120,22 @@
         <v>20</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -8155,13 +8160,13 @@
         <v>20</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
@@ -8179,34 +8184,34 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>20</v>
@@ -8214,10 +8219,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8225,10 +8230,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>20</v>
@@ -8237,22 +8242,22 @@
         <v>20</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -8301,45 +8306,45 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8347,10 +8352,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>20</v>
@@ -8362,19 +8367,19 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8399,13 +8404,13 @@
         <v>20</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>20</v>
@@ -8423,19 +8428,19 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>20</v>
@@ -8444,10 +8449,10 @@
         <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
@@ -8458,21 +8463,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
@@ -8484,19 +8489,19 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -8521,13 +8526,13 @@
         <v>20</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>20</v>
@@ -8545,45 +8550,45 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8591,10 +8596,10 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
@@ -8606,19 +8611,19 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -8667,19 +8672,19 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>20</v>
@@ -8688,10 +8693,10 @@
         <v>20</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>20</v>
@@ -8702,47 +8707,47 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -8791,19 +8796,19 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
@@ -8812,10 +8817,10 @@
         <v>20</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>20</v>
@@ -8826,10 +8831,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8837,10 +8842,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>20</v>
@@ -8852,13 +8857,13 @@
         <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8909,13 +8914,13 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>20</v>
@@ -8933,7 +8938,7 @@
         <v>20</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>20</v>
@@ -8944,21 +8949,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>20</v>
@@ -8970,16 +8975,16 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9029,19 +9034,19 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>20</v>
@@ -9053,7 +9058,7 @@
         <v>20</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>20</v>
@@ -9064,45 +9069,45 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -9151,19 +9156,19 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>20</v>
@@ -9175,7 +9180,7 @@
         <v>20</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>20</v>
@@ -9186,10 +9191,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9197,10 +9202,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>20</v>
@@ -9209,22 +9214,22 @@
         <v>20</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -9234,7 +9239,7 @@
         <v>20</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>20</v>
@@ -9249,13 +9254,13 @@
         <v>20</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>20</v>
@@ -9273,34 +9278,34 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>20</v>
@@ -9308,10 +9313,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9319,10 +9324,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
@@ -9331,22 +9336,22 @@
         <v>20</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -9395,45 +9400,45 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9441,10 +9446,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>20</v>
@@ -9456,13 +9461,13 @@
         <v>20</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9513,13 +9518,13 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>20</v>
@@ -9537,7 +9542,7 @@
         <v>20</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>20</v>
@@ -9548,21 +9553,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>20</v>
@@ -9574,16 +9579,16 @@
         <v>20</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9621,31 +9626,31 @@
         <v>20</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>20</v>
@@ -9657,7 +9662,7 @@
         <v>20</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>20</v>
@@ -9668,10 +9673,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9679,10 +9684,10 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>20</v>
@@ -9691,22 +9696,22 @@
         <v>20</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>20</v>
@@ -9755,19 +9760,19 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>20</v>
@@ -9776,10 +9781,10 @@
         <v>20</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>20</v>
@@ -9790,10 +9795,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9801,38 +9806,38 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q65" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="R65" t="s" s="2">
         <v>20</v>
@@ -9853,13 +9858,13 @@
         <v>20</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>20</v>
@@ -9877,19 +9882,19 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>20</v>
@@ -9898,10 +9903,10 @@
         <v>20</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>20</v>
@@ -9912,10 +9917,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9923,10 +9928,10 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>20</v>
@@ -9935,20 +9940,20 @@
         <v>20</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -9997,19 +10002,19 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>20</v>
@@ -10018,10 +10023,10 @@
         <v>20</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>20</v>
@@ -10032,10 +10037,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10043,10 +10048,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>20</v>
@@ -10055,20 +10060,20 @@
         <v>20</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>20</v>
@@ -10078,7 +10083,7 @@
         <v>20</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>20</v>
@@ -10117,19 +10122,19 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>20</v>
@@ -10138,10 +10143,10 @@
         <v>20</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>20</v>
@@ -10152,10 +10157,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10163,10 +10168,10 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>20</v>
@@ -10175,22 +10180,22 @@
         <v>20</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -10200,7 +10205,7 @@
         <v>20</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>20</v>
@@ -10239,19 +10244,19 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>20</v>
@@ -10260,10 +10265,10 @@
         <v>20</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>20</v>
@@ -10274,10 +10279,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10285,10 +10290,10 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>20</v>
@@ -10300,19 +10305,19 @@
         <v>20</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>20</v>
@@ -10337,13 +10342,13 @@
         <v>20</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>20</v>
@@ -10361,19 +10366,19 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>20</v>
@@ -10382,10 +10387,10 @@
         <v>20</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>20</v>
@@ -10396,21 +10401,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>20</v>
@@ -10422,19 +10427,19 @@
         <v>20</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>20</v>
@@ -10459,13 +10464,13 @@
         <v>20</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>20</v>
@@ -10483,45 +10488,45 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10529,10 +10534,10 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>20</v>
@@ -10544,19 +10549,19 @@
         <v>20</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>20</v>
@@ -10605,19 +10610,19 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>20</v>
@@ -10626,10 +10631,10 @@
         <v>20</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>20</v>
